--- a/task184/golden/harbourgate_slot_weights.xlsx
+++ b/task184/golden/harbourgate_slot_weights.xlsx
@@ -66,15 +66,15 @@
     <t>20:00 to 00:00</t>
   </si>
   <si>
+    <t>commissioned</t>
+  </si>
+  <si>
     <t>Tuesday</t>
   </si>
   <si>
     <t>Wednesday</t>
   </si>
   <si>
-    <t>commissioned</t>
-  </si>
-  <si>
     <t>Thursday</t>
   </si>
   <si>
@@ -87,28 +87,28 @@
     <t>Sunday</t>
   </si>
   <si>
-    <t>Saturday 20:00 to 00:00</t>
-  </si>
-  <si>
-    <t>Friday 20:00 to 00:00</t>
+    <t>Thursday 20:00 to 00:00</t>
+  </si>
+  <si>
+    <t>Saturday 00:00 to 04:00</t>
   </si>
   <si>
     <t>Sunday 00:00 to 04:00</t>
   </si>
   <si>
-    <t>Saturday 00:00 to 04:00</t>
-  </si>
-  <si>
-    <t>Sunday 04:00 to 08:00</t>
+    <t>Sunday 20:00 to 00:00</t>
+  </si>
+  <si>
+    <t>Friday 12:00 to 16:00</t>
   </si>
   <si>
     <t>Wednesday 20:00 to 00:00</t>
   </si>
   <si>
-    <t>Thursday 20:00 to 00:00</t>
-  </si>
-  <si>
-    <t>Saturday 04:00 to 08:00</t>
+    <t>Monday 20:00 to 00:00</t>
+  </si>
+  <si>
+    <t>Tuesday 20:00 to 00:00</t>
   </si>
   <si>
     <t>The eight together</t>
@@ -201,7 +201,7 @@
     <t>Population: offences of the classes at Annex B of the tasking agreement, at the five locations in harbourgate_location_register.csv, occurring between 1 April and 30 September in 2025 and in 2026.</t>
   </si>
   <si>
-    <t>Slot figures are one season, the mean of the two seasons on record, to the nearest fifty offences. An offence whose occurrence window touches more than one slot is counted into each in proportion to the share of the window falling in it.</t>
+    <t>Slot figures are one season, the mean of the two seasons on record, to the nearest fifty offences. An offence whose record gives only the earliest and the latest time it can have occurred is placed by the quarter's own hour-of-week clock, which is read off the windows themselves rather than assumed flat inside each one.</t>
   </si>
   <si>
     <t>The Cranstoun length of Harbourgate Street, above number 178, is outside the quarter and outside every figure here.</t>
@@ -277,15 +277,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -624,7 +625,7 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>250</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -635,7 +636,7 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -646,7 +647,7 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -657,7 +658,7 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>250</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -668,23 +669,26 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7">
-        <v>300</v>
+      <c r="C7" s="2">
+        <v>500</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
@@ -695,106 +699,109 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>6</v>
       </c>
       <c r="C9">
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
       </c>
       <c r="C10">
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
       </c>
       <c r="C11">
-        <v>250</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
       </c>
       <c r="C12">
-        <v>200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="2">
+        <v>500</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13">
-        <v>300</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>5</v>
       </c>
       <c r="C14">
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
         <v>6</v>
       </c>
       <c r="C15">
-        <v>150</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
         <v>7</v>
       </c>
       <c r="C16">
-        <v>250</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
         <v>8</v>
       </c>
       <c r="C17">
-        <v>250</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
@@ -805,16 +812,16 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="2">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -825,7 +832,7 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -836,7 +843,7 @@
         <v>6</v>
       </c>
       <c r="C21">
-        <v>250</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -847,7 +854,7 @@
         <v>7</v>
       </c>
       <c r="C22">
-        <v>250</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -858,7 +865,7 @@
         <v>8</v>
       </c>
       <c r="C23">
-        <v>250</v>
+        <v>350</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -869,7 +876,7 @@
         <v>9</v>
       </c>
       <c r="C24">
-        <v>250</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -879,11 +886,11 @@
       <c r="B25" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="2">
-        <v>400</v>
+      <c r="C25" s="3">
+        <v>1100</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -894,7 +901,7 @@
         <v>5</v>
       </c>
       <c r="C26">
-        <v>300</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -905,7 +912,7 @@
         <v>6</v>
       </c>
       <c r="C27">
-        <v>250</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -916,18 +923,21 @@
         <v>7</v>
       </c>
       <c r="C28">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="A29" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C29">
-        <v>300</v>
+      <c r="C29" s="2">
+        <v>550</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -938,21 +948,18 @@
         <v>9</v>
       </c>
       <c r="C30">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="A31" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="2">
-        <v>650</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>13</v>
+      <c r="C31">
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -963,24 +970,21 @@
         <v>5</v>
       </c>
       <c r="C32" s="2">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+      <c r="A33" t="s">
         <v>16</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="2">
-        <v>400</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>13</v>
+      <c r="C33">
+        <v>200</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -991,7 +995,7 @@
         <v>7</v>
       </c>
       <c r="C34">
-        <v>300</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1002,7 +1006,7 @@
         <v>8</v>
       </c>
       <c r="C35">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1017,17 +1021,14 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+      <c r="A37" t="s">
         <v>16</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="2">
-        <v>650</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>13</v>
+      <c r="C37">
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1038,24 +1039,21 @@
         <v>5</v>
       </c>
       <c r="C38" s="2">
-        <v>550</v>
+        <v>850</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+      <c r="A39" t="s">
         <v>17</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="2">
-        <v>450</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>13</v>
+      <c r="C39">
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1066,7 +1064,7 @@
         <v>7</v>
       </c>
       <c r="C40">
-        <v>250</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1077,7 +1075,7 @@
         <v>8</v>
       </c>
       <c r="C41">
-        <v>200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1088,18 +1086,21 @@
         <v>9</v>
       </c>
       <c r="C42">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="A43" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C43">
-        <v>350</v>
+      <c r="C43" s="2">
+        <v>800</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1128,8 +1129,8 @@
       <c r="A2" t="s">
         <v>18</v>
       </c>
-      <c r="B2">
-        <v>650</v>
+      <c r="B2" s="4">
+        <v>1100</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1137,7 +1138,7 @@
         <v>19</v>
       </c>
       <c r="B3">
-        <v>650</v>
+        <v>900</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1145,7 +1146,7 @@
         <v>20</v>
       </c>
       <c r="B4">
-        <v>550</v>
+        <v>850</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1153,7 +1154,7 @@
         <v>21</v>
       </c>
       <c r="B5">
-        <v>500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1161,7 +1162,7 @@
         <v>22</v>
       </c>
       <c r="B6">
-        <v>450</v>
+        <v>550</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1169,7 +1170,7 @@
         <v>23</v>
       </c>
       <c r="B7">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -1177,7 +1178,7 @@
         <v>24</v>
       </c>
       <c r="B8">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1185,15 +1186,15 @@
         <v>25</v>
       </c>
       <c r="B9">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="4">
-        <v>4050</v>
+      <c r="B10" s="6">
+        <v>5700</v>
       </c>
     </row>
   </sheetData>
@@ -1226,10 +1227,10 @@
       <c r="A2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>2025</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="4">
         <v>2520</v>
       </c>
     </row>
@@ -1237,10 +1238,10 @@
       <c r="A3" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <v>2026</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
         <v>2680</v>
       </c>
     </row>
@@ -1248,10 +1249,10 @@
       <c r="A4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>2025</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>2040</v>
       </c>
     </row>
@@ -1259,10 +1260,10 @@
       <c r="A5" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>2026</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
         <v>2160</v>
       </c>
     </row>
@@ -1270,10 +1271,10 @@
       <c r="A6" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>2025</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <v>3690</v>
       </c>
     </row>
@@ -1281,10 +1282,10 @@
       <c r="A7" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>2026</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
         <v>3910</v>
       </c>
     </row>
@@ -1292,10 +1293,10 @@
       <c r="A8" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>2025</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="4">
         <v>2580</v>
       </c>
     </row>
@@ -1303,10 +1304,10 @@
       <c r="A9" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>2026</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="4">
         <v>2740</v>
       </c>
     </row>
@@ -1314,10 +1315,10 @@
       <c r="A10" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>2025</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <v>1310</v>
       </c>
     </row>
@@ -1325,10 +1326,10 @@
       <c r="A11" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="4">
         <v>2026</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="4">
         <v>1390</v>
       </c>
     </row>
@@ -1336,7 +1337,7 @@
       <c r="A12" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>2025</v>
       </c>
       <c r="C12">
@@ -1347,7 +1348,7 @@
       <c r="A13" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="4">
         <v>2026</v>
       </c>
       <c r="C13">
@@ -1358,10 +1359,10 @@
       <c r="A14" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>2025</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="4">
         <v>1150</v>
       </c>
     </row>
@@ -1369,10 +1370,10 @@
       <c r="A15" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="4">
         <v>2026</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="4">
         <v>1220</v>
       </c>
     </row>
@@ -1380,10 +1381,10 @@
       <c r="A16" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <v>2025</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="4">
         <v>1420</v>
       </c>
     </row>
@@ -1391,10 +1392,10 @@
       <c r="A17" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>2026</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="4">
         <v>1510</v>
       </c>
     </row>
@@ -1402,10 +1403,10 @@
       <c r="A18" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>2025</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="4">
         <v>2170</v>
       </c>
     </row>
@@ -1413,10 +1414,10 @@
       <c r="A19" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="4">
         <v>2026</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="4">
         <v>2310</v>
       </c>
     </row>
@@ -1450,54 +1451,54 @@
       <c r="A2" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>2025</v>
       </c>
-      <c r="C2" s="6">
-        <v>36.1</v>
+      <c r="C2" s="7">
+        <v>35.8</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <v>2026</v>
       </c>
-      <c r="C3" s="6">
-        <v>35.1</v>
+      <c r="C3" s="7">
+        <v>35.7</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>2025</v>
       </c>
-      <c r="C4" s="6">
-        <v>13.4</v>
+      <c r="C4" s="7">
+        <v>13.8</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>2026</v>
       </c>
-      <c r="C5" s="6">
-        <v>14</v>
+      <c r="C5" s="7">
+        <v>13.8</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>2025</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="7">
         <v>19.3</v>
       </c>
     </row>
@@ -1505,55 +1506,55 @@
       <c r="A7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>2026</v>
       </c>
-      <c r="C7" s="6">
-        <v>19.5</v>
+      <c r="C7" s="7">
+        <v>19.8</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>2025</v>
       </c>
-      <c r="C8" s="6">
-        <v>21.1</v>
+      <c r="C8" s="7">
+        <v>21.2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>2026</v>
       </c>
-      <c r="C9" s="6">
-        <v>21.4</v>
+      <c r="C9" s="7">
+        <v>21.1</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>45</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>2025</v>
       </c>
-      <c r="C10" s="6">
-        <v>10.1</v>
+      <c r="C10" s="7">
+        <v>9.9</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="4">
         <v>2026</v>
       </c>
-      <c r="C11" s="6">
-        <v>10</v>
+      <c r="C11" s="7">
+        <v>9.6</v>
       </c>
     </row>
   </sheetData>
@@ -1586,10 +1587,10 @@
       <c r="A2" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>2025</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="4">
         <v>1320</v>
       </c>
     </row>
@@ -1597,10 +1598,10 @@
       <c r="A3" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <v>2026</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
         <v>1380</v>
       </c>
     </row>
@@ -1608,7 +1609,7 @@
       <c r="A4" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>2025</v>
       </c>
       <c r="C4">
@@ -1619,29 +1620,29 @@
       <c r="A5" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>2026</v>
       </c>
       <c r="C5">
-        <v>890</v>
+        <v>900</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>2025</v>
       </c>
       <c r="C6">
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>2026</v>
       </c>
       <c r="C7">
@@ -1652,7 +1653,7 @@
       <c r="A8" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>2025</v>
       </c>
       <c r="C8">
@@ -1663,7 +1664,7 @@
       <c r="A9" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>2026</v>
       </c>
       <c r="C9">
@@ -1684,52 +1685,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="9" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="9" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="9" t="s">
         <v>61</v>
       </c>
     </row>
